--- a/assets/master_spd.xlsx
+++ b/assets/master_spd.xlsx
@@ -1263,7 +1263,6 @@
     <col min="15" max="15" width="2.109375" customWidth="1"/>
     <col min="16" max="16" width="13.44140625" customWidth="1"/>
     <col min="17" max="17" width="20.5546875" customWidth="1"/>
-    <col min="18" max="26" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
